--- a/test_questionnaires/HealthPlus_HIPAA_Security_Review_2026.xlsx
+++ b/test_questionnaires/HealthPlus_HIPAA_Security_Review_2026.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,10 +28,21 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="11"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <color rgb="00666666"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <sz val="10"/>
+    </font>
+    <font>
+      <color rgb="00333333"/>
+      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -40,18 +51,21 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="003F51B5"/>
-        <bgColor rgb="003F51B5"/>
+        <fgColor rgb="001E3A5F"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F5F5FF"/>
-        <bgColor rgb="00F5F5FF"/>
+        <fgColor rgb="00F5F7FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -59,20 +73,53 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <right style="thin">
+        <color rgb="00CCCCCC"/>
+      </right>
+      <bottom style="thin">
+        <color rgb="00CCCCCC"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="00E0E0E0"/>
+      </right>
+      <bottom style="thin">
+        <color rgb="00E0E0E0"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -440,15 +487,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="72" customWidth="1" min="2" max="2"/>
-    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>#</t>
@@ -461,163 +509,255 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Answer</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="40" customHeight="1">
-      <c r="A2" t="n">
+          <t>Response
+(Yes / No / Partial / N-A)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Comments / Evidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="45" customHeight="1">
+      <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Do you have a signed Business Associate Agreement (BAA) process? Describe how you handle BAAs.</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3" ht="40" customHeight="1">
-      <c r="A3" s="3" t="n">
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Are you willing and able to sign a Business Associate Agreement (BAA) before accessing any PHI?</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr"/>
+      <c r="D2" s="5" t="inlineStr"/>
+    </row>
+    <row r="3" ht="45" customHeight="1">
+      <c r="A3" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>How is Protected Health Information (PHI) encrypted at rest and in transit?</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr"/>
-    </row>
-    <row r="4" ht="40" customHeight="1">
-      <c r="A4" t="n">
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Do you have documented HIPAA compliance policies covering the Privacy Rule and Security Rule?</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr"/>
+      <c r="D3" s="9" t="inlineStr"/>
+    </row>
+    <row r="4" ht="45" customHeight="1">
+      <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Describe your access control policies for staff who may access PHI.</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr"/>
-    </row>
-    <row r="5" ht="40" customHeight="1">
-      <c r="A5" s="3" t="n">
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Is Protected Health Information (PHI) encrypted at rest using AES-256 or equivalent?</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr"/>
+      <c r="D4" s="5" t="inlineStr"/>
+    </row>
+    <row r="5" ht="45" customHeight="1">
+      <c r="A5" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>What audit logging do you maintain for access to systems containing PHI?</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr"/>
-    </row>
-    <row r="6" ht="40" customHeight="1">
-      <c r="A6" t="n">
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Is PHI encrypted in transit using TLS 1.2 or higher on all connections?</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr"/>
+      <c r="D5" s="9" t="inlineStr"/>
+    </row>
+    <row r="6" ht="45" customHeight="1">
+      <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>How do you handle and report breaches involving PHI under HIPAA Breach Notification Rule?</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr"/>
-    </row>
-    <row r="7" ht="40" customHeight="1">
-      <c r="A7" s="3" t="n">
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Do you conduct and document a formal HIPAA Risk Analysis at least annually?</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr"/>
+      <c r="D6" s="5" t="inlineStr"/>
+    </row>
+    <row r="7" ht="45" customHeight="1">
+      <c r="A7" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Do you perform a HIPAA Security Risk Assessment? How frequently?</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr"/>
-    </row>
-    <row r="8" ht="40" customHeight="1">
-      <c r="A8" t="n">
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Is access to PHI restricted to workforce members with a documented minimum-necessary business need?</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr"/>
+      <c r="D7" s="9" t="inlineStr"/>
+    </row>
+    <row r="8" ht="45" customHeight="1">
+      <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>How do you ensure PHI is not retained beyond its required retention period?</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr"/>
-    </row>
-    <row r="9" ht="40" customHeight="1">
-      <c r="A9" s="3" t="n">
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Do you maintain a complete audit log of all access, modification, and transmission of PHI?</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr"/>
+      <c r="D8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9" ht="45" customHeight="1">
+      <c r="A9" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Describe your workforce training program specific to HIPAA requirements.</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr"/>
-    </row>
-    <row r="10" ht="40" customHeight="1">
-      <c r="A10" t="n">
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Do you have automatic session timeouts for workstations that may access PHI?</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr"/>
+      <c r="D9" s="9" t="inlineStr"/>
+    </row>
+    <row r="10" ht="45" customHeight="1">
+      <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>What physical security controls protect systems that store or process PHI?</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr"/>
-    </row>
-    <row r="11" ht="40" customHeight="1">
-      <c r="A11" s="3" t="n">
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Are workforce members with access to PHI trained on HIPAA requirements upon hire and annually thereafter?</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr"/>
+      <c r="D10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11" ht="45" customHeight="1">
+      <c r="A11" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>How do you manage access for business associates and subcontractors who access PHI?</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr"/>
-    </row>
-    <row r="12" ht="40" customHeight="1">
-      <c r="A12" t="n">
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Do you have a documented process for responding to and notifying customers of a PHI breach within 60 days?</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr"/>
+      <c r="D11" s="9" t="inlineStr"/>
+    </row>
+    <row r="12" ht="45" customHeight="1">
+      <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Do you have documented policies for workstation use and device security for PHI access?</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr"/>
-    </row>
-    <row r="13" ht="40" customHeight="1">
-      <c r="A13" s="3" t="n">
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Have you experienced any PHI breaches reportable under HIPAA in the past 24 months?</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr"/>
+      <c r="D12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13" ht="45" customHeight="1">
+      <c r="A13" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>How do you handle portable media and mobile devices that may contain PHI?</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr"/>
-    </row>
-    <row r="14" ht="40" customHeight="1">
-      <c r="A14" t="n">
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Are mobile devices that may store or access PHI subject to MDM controls including remote wipe?</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr"/>
+      <c r="D13" s="9" t="inlineStr"/>
+    </row>
+    <row r="14" ht="45" customHeight="1">
+      <c r="A14" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>What is your incident response procedure specific to PHI breaches?</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr"/>
-    </row>
-    <row r="15" ht="40" customHeight="1">
-      <c r="A15" s="3" t="n">
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Do you ensure that all subcontractors who may access PHI also sign a BAA with you?</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr"/>
+      <c r="D14" s="5" t="inlineStr"/>
+    </row>
+    <row r="15" ht="45" customHeight="1">
+      <c r="A15" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>Describe your data backup and disaster recovery procedures for PHI systems.</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr"/>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Is PHI stored in dedicated, access-controlled storage systems separate from other data?</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr"/>
+      <c r="D15" s="9" t="inlineStr"/>
+    </row>
+    <row r="16" ht="45" customHeight="1">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Do you perform regular testing of your HIPAA incident response procedures?</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr"/>
+      <c r="D16" s="5" t="inlineStr"/>
+    </row>
+    <row r="17" ht="45" customHeight="1">
+      <c r="A17" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Can you provide a list of all locations (data centres, cloud regions) where PHI may be stored or processed?</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr"/>
+      <c r="D17" s="9" t="inlineStr"/>
+    </row>
+    <row r="18" ht="45" customHeight="1">
+      <c r="A18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Do you have controls preventing PHI from being stored in email, chat logs, or unsecured endpoints?</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr"/>
+      <c r="D18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19" ht="45" customHeight="1">
+      <c r="A19" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Is a sanction policy in place for workforce members who violate HIPAA policies?</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr"/>
+      <c r="D19" s="9" t="inlineStr"/>
+    </row>
+    <row r="20" ht="45" customHeight="1">
+      <c r="A20" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>How long do you retain PHI after the end of the business relationship, and how is it securely disposed of?</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr"/>
+      <c r="D20" s="5" t="inlineStr"/>
+    </row>
+    <row r="21" ht="45" customHeight="1">
+      <c r="A21" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>Do you have a documented backup and recovery process for systems containing PHI?</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr"/>
+      <c r="D21" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
